--- a/artfynd/A 32465-2025 artfynd.xlsx
+++ b/artfynd/A 32465-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90848664</v>
+        <v>90848798</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445541.7973386805</v>
+        <v>445633</v>
       </c>
       <c r="R2" t="n">
-        <v>7039207.210809185</v>
+        <v>7039295</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Möjlig kalkbarrskog</t>
+          <t>Kalkbarrskog</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Andreas Karlsson Tiselius</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,12 +789,7 @@
         <v>90848663</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445565.0688836736</v>
+        <v>445565</v>
       </c>
       <c r="R3" t="n">
-        <v>7039206.813612641</v>
+        <v>7039207</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90921649</v>
+        <v>90848664</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445591.1206192054</v>
+        <v>445542</v>
       </c>
       <c r="R4" t="n">
-        <v>7039343.16634184</v>
+        <v>7039207</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,26 +965,11 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt med blåsippa</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1029,9 +979,14 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Andreas Karlsson Tiselius</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91133007</v>
+        <v>90848669</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,14 +1039,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Storvallen-Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445627.1080308883</v>
+        <v>445504</v>
       </c>
       <c r="R5" t="n">
-        <v>7039300.977723569</v>
+        <v>7039194</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,21 +1076,11 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1152,12 +1092,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog</t>
+          <t>Möjlig kalkbarrskog</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Andreas Karlsson Tiselius</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1179,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91132971</v>
+        <v>90921649</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,17 +1150,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Halbodarna_SÖ, Jmt</t>
+          <t>Storvallen-Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445589.855199319</v>
+        <v>445591</v>
       </c>
       <c r="R6" t="n">
-        <v>7039268.97841838</v>
+        <v>7039343</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,19 +1187,14 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt med blåsippa</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,11 +1205,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -1305,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91132982</v>
+        <v>91132971</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445611.8446891078</v>
+        <v>445590</v>
       </c>
       <c r="R7" t="n">
-        <v>7039272.179822366</v>
+        <v>7039269</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1378,19 +1298,9 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-08-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,15 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91133005</v>
+        <v>91132982</v>
       </c>
       <c r="B8" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445623.8763773348</v>
+        <v>445612</v>
       </c>
       <c r="R8" t="n">
-        <v>7039295.221210113</v>
+        <v>7039272</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1504,19 +1409,9 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1560,12 +1455,7 @@
         <v>91132991</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1597,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445606.8042410974</v>
+        <v>445607</v>
       </c>
       <c r="R9" t="n">
-        <v>7039317.864527171</v>
+        <v>7039318</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1630,19 +1520,9 @@
           <t>2019-08-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-08-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1676,6 +1556,450 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91132994</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>445643</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039282</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>91133000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>445611</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7039238</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>91133005</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>445624</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7039295</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>91133007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Halbodarna_SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>445627</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7039301</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-08-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Andreas Karlsson Tiselius</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>

--- a/artfynd/A 32465-2025 artfynd.xlsx
+++ b/artfynd/A 32465-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848663</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848664</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848669</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921649</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132971</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132982</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132991</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91132994</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133005</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,8 +2064,27 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91133007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>